--- a/new_model/model_Fe_Si_B_260311/scmace_0.0001_40_10_rnd_e/test_res/model_rnd_e_scmace_lr0.0001_40_10_test.xlsx
+++ b/new_model/model_Fe_Si_B_260311/scmace_0.0001_40_10_rnd_e/test_res/model_rnd_e_scmace_lr0.0001_40_10_test.xlsx
@@ -27018,10 +27018,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6361515499368963</v>
+        <v>636.1515499368962</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3359071278754407</v>
+        <v>335.9071278754407</v>
       </c>
       <c r="E4" t="n">
         <v>0.9482201863766788</v>
@@ -27037,10 +27037,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.4841121196188106</v>
+        <v>484.1121196188106</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3370154075451501</v>
+        <v>337.0154075451501</v>
       </c>
       <c r="E5" t="n">
         <v>0.9697174825909621</v>
